--- a/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
+++ b/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6688105-2C17-4E37-9015-109A86479B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F383AC-5211-4BBA-B610-7265FE959CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="6" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Attila the Hun" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="307">
   <si>
     <t>Scenario</t>
   </si>
@@ -3096,91 +3096,6 @@
       </rPr>
       <t xml:space="preserve">
 Starting Units:
-1 Scout Cavalry
-Later:
-8 Paladins (12 in Imperial Age)
-15 Heavy Cavalry Archers (20 in Imperial Age)
-4 Mangonels
-3 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:Identical to Moderate
-Later:
-6 Paladins (10 in Imperial Age)
-10 Heavy Cavalry Archers (15 in Imperial Age)
-2 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:Identical to Moderate
-Later:
-8 Paladins (15 in Imperial Age)
-15 Heavy Cavalry Archers (25 in Imperial Age)
-4 Mangonels
-3 Trebuchets</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:
 8 Men-at Arms
 4 Knights
 1 Scout Cavalry
@@ -3245,188 +3160,6 @@
 15 Champions
 8 Cavalier
 4 Petards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:
-7 Long Swordsmen
-5 Knights
-1 Light Cavalry
-Later:
-20 Legionaries
-15 Elite Centurions
-4 Scorpions
-4 Petards
-4 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:Identical to Moderate
-Later:
-8 Legionaries
-6 Elite Centurions
-2 Scorpions
-4 Petards
-2 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:Identical to Moderate
-Later:
-30 Legionaries
-22 Elite Centurions
-8 Scorpions
-4 Petards
-4 Trebuchets</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:
-10 Men-at-Arms
-4 Pikemen
-1 Scout Cavalry
-Later:
-20 Champions
-15 Halberdiers
-15 Elite Huskarls
-6 Capped Rams
-4 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:Identical to Moderate
-Later:
-15 Long Swordsmen
-10 Pikemen
-8 Huskarls
-3 Battering Rams
-2 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Starting Units:Identical to Moderate
-Later:
-30 Champions
-20 Halberdiers
-20 Elite Huskarls
-6 Capped Rams
-5 Trebuchets</t>
     </r>
   </si>
   <si>
@@ -4737,12 +4470,846 @@
 OR
 - GreenGold</t>
   </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Iron Boar</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Dire Wolf</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Bleda the Hun</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Tarkan</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>No items required
+Convert's to Player with 'Bleda's Base'</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>No items required
+Convert's to Player with 'Bleda's Base'
+ONLY available here, maybe keep one from converting to the Player?</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Manguai</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Scythian Scout</t>
+  </si>
+  <si>
+    <t>War Elephant</t>
+  </si>
+  <si>
+    <t>Requires EITHER
+- Bleda's Base
+OR
+- Attilla's Base
++ Town Center Wood/Stone
+AND
+Dock</t>
+  </si>
+  <si>
+    <t>Fishing Boat</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Requires EITHER
+- Bleda's Base
+OR
+- Attilla's Base
++ Town Center Wood/Stone
+AND
+Dock
+OR
+Castle
+OR
+Tower</t>
+  </si>
+  <si>
+    <t>Yurt</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Chain</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Yurt (Large)</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Hunting Wolf</t>
+  </si>
+  <si>
+    <t>Scythian Wild Woman</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Spearman
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mangonel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pikemen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Long Swordsman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Requires 
+- Purple Villagers
++ Town Center Wood/Stone
++ Dock</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Fish Trap</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Wild Horse</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Pikeman
+(not on Standard)</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Trade Cog</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Cataphract</t>
+  </si>
+  <si>
+    <t>Requires
+Dock</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Sea Gate</t>
+  </si>
+  <si>
+    <t>Requires
+Town Center</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Elite Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Scorpion
+(not on Standard)</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>Legionary</t>
+  </si>
+  <si>
+    <t>Elite Centurion</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion
+(not on Standard)</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+7 Long Swordsmen
+5 Knights
+1 Light Cavalry
+Later:
+20 Legionaries
+15 Elite Centurions
+4 Scorpions
+4 Petards
+4 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+Identical to Moderate
+Later:
+8 Legionaries
+6 Elite Centurions
+2 Scorpions
+4 Petards
+2 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+Identical to Moderate
+Later:
+30 Legionaries
+22 Elite Centurions
+8 Scorpions
+4 Petards
+4 Trebuchets</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+10 Men-at-Arms
+4 Pikemen
+1 Scout Cavalry
+Later:
+20 Champions
+15 Halberdiers
+15 Elite Huskarls
+6 Capped Rams
+4 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+Identical to Moderate
+Later:
+15 Long Swordsmen
+10 Pikemen
+8 Huskarls
+3 Battering Rams
+2 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+Identical to Moderate
+Later:
+30 Champions
+20 Halberdiers
+20 Elite Huskarls
+6 Capped Rams
+5 Trebuchets</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+1 Scout Cavalry
+Later:
+8 Paladins (12 in Imperial Age)
+15 Heavy Cavalry Archers (20 in Imperial Age)
+4 Mangonels
+3 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+Identical to Moderate
+Later:
+6 Paladins (10 in Imperial Age)
+10 Heavy Cavalry Archers (15 in Imperial Age)
+2 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Starting Units:
+Identical to Moderate
+Later:
+8 Paladins (15 in Imperial Age)
+15 Heavy Cavalry Archers (25 in Imperial Age)
+4 Mangonels
+3 Trebuchets</t>
+    </r>
+  </si>
+  <si>
+    <t>Huskarl</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Halberdier
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two-Handed Swordsman
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Champion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Huskarl
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Capped Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mangonel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Centurion</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Petard</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Pavillions</t>
+  </si>
+  <si>
+    <t>Goat</t>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Siege Onager
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Longbowman</t>
+  </si>
+  <si>
+    <t>Pope Leo I</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Amphitheatre</t>
+  </si>
+  <si>
+    <t>Arch of Constantine</t>
+  </si>
+  <si>
+    <t>Aqueduct</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4903,6 +5470,68 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2FE2F5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4912,7 +5541,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -5030,11 +5659,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5076,6 +5753,93 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5469,7 +6233,7 @@
         <v>43</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5514,7 +6278,7 @@
         <v>46</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5565,7 +6329,7 @@
         <v>58</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5605,10 +6369,10 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5653,7 +6417,7 @@
         <v>69</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="2:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5673,19 +6437,19 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>74</v>
+        <v>282</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>73</v>
@@ -5694,7 +6458,7 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:18" ht="408.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5714,30 +6478,30 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="M9" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -5748,249 +6512,575 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF25A3-39E5-43BC-AA21-825EC7632C75}">
-  <dimension ref="B1:D23"/>
+  <dimension ref="B1:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.140625" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="93.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="C5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="C6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="C7" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
+      <c r="C8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="C9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
+      <c r="C10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="C11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="C12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="C13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
+      <c r="C14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
+      <c r="C15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+      <c r="C16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+      <c r="C17" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
+      <c r="C18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
+      <c r="C19" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
+      <c r="C20" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
+      <c r="C21" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B20" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="14" t="s">
-        <v>114</v>
-      </c>
       <c r="C22" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" s="14"/>
       <c r="C23" s="8"/>
+      <c r="K23" s="19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="225" x14ac:dyDescent="0.25">
+      <c r="G24" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="G25" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="K26" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="K27" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+    </row>
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+    </row>
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+    </row>
+    <row r="33" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+    </row>
+    <row r="34" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+    </row>
+    <row r="35" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -6000,193 +7090,473 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC364C8-CB39-4783-9CFD-864E580ACCC1}">
-  <dimension ref="B1:D18"/>
+  <dimension ref="B1:L25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="4" width="23" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="C7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
+      <c r="C8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="C9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
+      <c r="C10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
-        <v>128</v>
-      </c>
       <c r="C18" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K20" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="25"/>
+      <c r="K21" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="25"/>
+      <c r="K22" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="25"/>
+      <c r="K23" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K24" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="K25" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -6196,349 +7566,979 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00C403-3C77-4C50-8FD7-B532FB244FE1}">
-  <dimension ref="B1:D21"/>
+  <dimension ref="B1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="23.140625" customWidth="1"/>
     <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="G13" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="C14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
+      <c r="C15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="C16" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+      <c r="G16" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+      <c r="C17" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
+      <c r="C18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="D20" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K24" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K25" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K26" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K27" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K28" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA707A4-84AD-4A37-9A2B-76628AC8689E}">
-  <dimension ref="B1:D10"/>
+  <dimension ref="B1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.140625" customWidth="1"/>
     <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="93.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="34" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="L3" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="C7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
+      <c r="C8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="C9" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>151</v>
-      </c>
       <c r="C10" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K19" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K22" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+    </row>
+    <row r="24" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="N25" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="26" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+    </row>
+    <row r="27" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+    </row>
+    <row r="28" spans="7:14" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -6547,91 +8547,528 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19264B5D-9C82-4108-AEE9-967C34FA97B5}">
-  <dimension ref="B1:D8"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5703125" customWidth="1"/>
     <col min="3" max="3" width="22.28515625" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="93.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="C4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="132" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="132" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="20" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>115</v>
-      </c>
+      <c r="L10" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K19" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -6640,170 +9077,548 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0107F7F4-65A4-4F3B-ABD6-BF0903CF1797}">
-  <dimension ref="B1:D15"/>
+  <dimension ref="B1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="300" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="300" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K3" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="C7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
+      <c r="C8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="C9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
+      <c r="C10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="C11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="C12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="C13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="300" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>166</v>
-      </c>
       <c r="C14" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="318.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="K26" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="K28" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="L28" s="36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="H29" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
+++ b/docs/Logic Requirements/Ageipelago Attila the Hun.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F383AC-5211-4BBA-B610-7265FE959CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6984C88F-F72A-45E1-B416-A20AE792BBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="6" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Attila the Hun" sheetId="1" r:id="rId1"/>
@@ -4653,20 +4653,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Spearman
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(not on Hard)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="14"/>
         <color rgb="FF0070C0"/>
@@ -4771,10 +4757,6 @@
   </si>
   <si>
     <t>Crossbowman</t>
-  </si>
-  <si>
-    <t>Pikeman
-(not on Standard)</t>
   </si>
   <si>
     <t>Trade Cart</t>
@@ -5154,21 +5136,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Two-Handed Swordsman
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(not on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Champion
 </t>
     </r>
@@ -5184,21 +5151,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Elite Huskarl
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(not on Standard)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Capped Ram
 </t>
     </r>
@@ -5303,6 +5255,112 @@
   </si>
   <si>
     <t>Aqueduct</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pikeman
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Spearman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elite Huskarl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Two-Handed Swordsman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5711,7 +5769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5825,9 +5883,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6443,13 +6498,13 @@
         <v>74</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="M8" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>73</v>
@@ -6559,7 +6614,7 @@
       <c r="H3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="17" t="s">
         <v>212</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -6622,7 +6677,7 @@
       <c r="D6" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="9" t="s">
         <v>189</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -6645,7 +6700,7 @@
       <c r="D7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="16" t="s">
         <v>190</v>
       </c>
       <c r="H7" s="8" t="s">
@@ -6927,7 +6982,7 @@
       <c r="H19" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="K19" s="22" t="s">
+      <c r="K19" s="20" t="s">
         <v>227</v>
       </c>
       <c r="L19" s="8" t="s">
@@ -6997,7 +7052,7 @@
         <v>207</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>165</v>
@@ -7252,7 +7307,7 @@
         <v>112</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>112</v>
@@ -7275,13 +7330,13 @@
         <v>112</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>112</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>112</v>
@@ -7303,7 +7358,7 @@
       <c r="H10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K10" s="30" t="s">
+      <c r="K10" s="28" t="s">
         <v>227</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -7407,7 +7462,7 @@
         <v>182</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>181</v>
@@ -7430,7 +7485,7 @@
         <v>112</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>181</v>
@@ -7453,7 +7508,7 @@
         <v>112</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>181</v>
@@ -7476,7 +7531,7 @@
         <v>112</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>181</v>
@@ -7507,7 +7562,7 @@
         <v>208</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K20" s="27" t="s">
         <v>225</v>
@@ -7544,8 +7599,8 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K24" s="18" t="s">
-        <v>246</v>
+      <c r="K24" s="17" t="s">
+        <v>245</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>112</v>
@@ -7553,7 +7608,7 @@
     </row>
     <row r="25" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="K25" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>181</v>
@@ -7637,7 +7692,7 @@
         <v>112</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>112</v>
@@ -7660,7 +7715,7 @@
         <v>112</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>112</v>
@@ -7706,7 +7761,7 @@
         <v>112</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>112</v>
@@ -7734,8 +7789,8 @@
       <c r="H8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K8" s="23" t="s">
-        <v>246</v>
+      <c r="K8" s="21" t="s">
+        <v>245</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>112</v>
@@ -7798,7 +7853,7 @@
         <v>112</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>112</v>
@@ -7821,7 +7876,7 @@
         <v>112</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>252</v>
+        <v>303</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>112</v>
@@ -7844,7 +7899,7 @@
         <v>167</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>112</v>
@@ -7916,7 +7971,7 @@
         <v>208</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>218</v>
@@ -7936,10 +7991,10 @@
         <v>170</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K17" s="20" t="s">
         <v>223</v>
@@ -7959,10 +8014,10 @@
         <v>112</v>
       </c>
       <c r="G18" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>257</v>
       </c>
       <c r="K18" s="20" t="s">
         <v>224</v>
@@ -7982,7 +8037,7 @@
         <v>112</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>112</v>
@@ -8005,7 +8060,7 @@
         <v>170</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>112</v>
@@ -8022,7 +8077,7 @@
         <v>112</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>112</v>
@@ -8030,7 +8085,7 @@
     </row>
     <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K22" s="19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>112</v>
@@ -8062,23 +8117,23 @@
     </row>
     <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K26" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K27" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K28" s="19" t="s">
         <v>261</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K27" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K28" s="31" t="s">
-        <v>263</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>112</v>
@@ -8209,7 +8264,7 @@
         <v>177</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>112</v>
@@ -8255,10 +8310,10 @@
         <v>176</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>214</v>
@@ -8278,10 +8333,10 @@
         <v>171</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K9" s="17" t="s">
         <v>233</v>
@@ -8301,10 +8356,10 @@
         <v>112</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K10" s="17" t="s">
         <v>216</v>
@@ -8315,10 +8370,10 @@
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G11" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>217</v>
@@ -8329,10 +8384,10 @@
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G12" s="26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K12" s="17" t="s">
         <v>220</v>
@@ -8346,10 +8401,10 @@
         <v>203</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>112</v>
@@ -8357,10 +8412,10 @@
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G14" s="26" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>230</v>
@@ -8371,10 +8426,10 @@
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G15" s="26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K15" s="21" t="s">
         <v>223</v>
@@ -8385,10 +8440,10 @@
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G16" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K16" s="21" t="s">
         <v>218</v>
@@ -8399,10 +8454,10 @@
     </row>
     <row r="17" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G17" s="26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K17" s="21" t="s">
         <v>228</v>
@@ -8416,7 +8471,7 @@
         <v>235</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K18" s="26" t="s">
         <v>213</v>
@@ -8427,10 +8482,10 @@
     </row>
     <row r="19" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G19" s="26" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K19" s="26" t="s">
         <v>231</v>
@@ -8441,13 +8496,13 @@
     </row>
     <row r="20" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G20" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>112</v>
@@ -8455,13 +8510,13 @@
     </row>
     <row r="21" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G21" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K21" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>112</v>
@@ -8469,13 +8524,13 @@
     </row>
     <row r="22" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G22" s="26" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K22" s="35" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L22" s="32" t="s">
         <v>112</v>
@@ -8483,53 +8538,53 @@
     </row>
     <row r="23" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
     </row>
     <row r="24" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
     </row>
     <row r="25" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
       <c r="N25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:14" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K27" s="25"/>
       <c r="L27" s="25"/>
@@ -8618,7 +8673,7 @@
         <v>177</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>112</v>
@@ -8670,7 +8725,7 @@
         <v>112</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>112</v>
@@ -8710,7 +8765,7 @@
         <v>112</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>112</v>
@@ -8730,7 +8785,7 @@
         <v>112</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>112</v>
@@ -8752,7 +8807,7 @@
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G11" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>112</v>
@@ -8766,7 +8821,7 @@
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G12" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>112</v>
@@ -8780,13 +8835,13 @@
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G13" s="22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>112</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>112</v>
@@ -8794,7 +8849,7 @@
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G14" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>112</v>
@@ -8808,7 +8863,7 @@
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G15" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>112</v>
@@ -8822,7 +8877,7 @@
     </row>
     <row r="16" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G16" s="20" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>112</v>
@@ -8836,12 +8891,12 @@
     </row>
     <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G17" s="20" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="26" t="s">
         <v>227</v>
       </c>
       <c r="L17" s="8" t="s">
@@ -8850,7 +8905,7 @@
     </row>
     <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G18" s="20" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>112</v>
@@ -8864,7 +8919,7 @@
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G19" s="20" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>112</v>
@@ -8892,13 +8947,13 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="26" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K21" s="40" t="s">
-        <v>295</v>
+      <c r="K21" s="39" t="s">
+        <v>291</v>
       </c>
       <c r="L21" s="32" t="s">
         <v>112</v>
@@ -8906,7 +8961,7 @@
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="35" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H22" s="32" t="s">
         <v>112</v>
@@ -8926,7 +8981,7 @@
     </row>
     <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="26" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>112</v>
@@ -8936,7 +8991,7 @@
     </row>
     <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="20" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>112</v>
@@ -8955,8 +9010,8 @@
       <c r="L26" s="25"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="19" t="s">
-        <v>291</v>
+      <c r="G27" s="31" t="s">
+        <v>287</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>112</v>
@@ -8966,7 +9021,7 @@
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>112</v>
@@ -8976,7 +9031,7 @@
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>112</v>
@@ -8986,7 +9041,7 @@
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="19" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>112</v>
@@ -8996,7 +9051,7 @@
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="24" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>112</v>
@@ -9130,8 +9185,8 @@
       <c r="H3" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="42" t="s">
-        <v>258</v>
+      <c r="K3" s="41" t="s">
+        <v>256</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>112</v>
@@ -9154,7 +9209,7 @@
         <v>112</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L4" s="9" t="s">
         <v>112</v>
@@ -9171,13 +9226,13 @@
         <v>178</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>112</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>112</v>
@@ -9194,13 +9249,13 @@
         <v>178</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="K6" s="23" t="s">
-        <v>262</v>
+      <c r="K6" s="21" t="s">
+        <v>260</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>112</v>
@@ -9222,8 +9277,8 @@
       <c r="H7" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="K7" s="23" t="s">
-        <v>263</v>
+      <c r="K7" s="21" t="s">
+        <v>261</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>112</v>
@@ -9263,7 +9318,7 @@
         <v>178</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>112</v>
@@ -9286,7 +9341,7 @@
         <v>178</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>112</v>
@@ -9332,13 +9387,13 @@
         <v>178</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>112</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>112</v>
@@ -9355,7 +9410,7 @@
         <v>178</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>112</v>
@@ -9378,7 +9433,7 @@
         <v>178</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>112</v>
@@ -9401,7 +9456,7 @@
         <v>112</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>112</v>
@@ -9415,7 +9470,7 @@
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G16" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>112</v>
@@ -9443,7 +9498,7 @@
     </row>
     <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G18" s="20" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>112</v>
@@ -9457,7 +9512,7 @@
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G19" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>112</v>
@@ -9471,13 +9526,13 @@
     </row>
     <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G20" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>112</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>112</v>
@@ -9485,7 +9540,7 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="18" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>112</v>
@@ -9499,13 +9554,13 @@
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="17" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>112</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>112</v>
@@ -9527,7 +9582,7 @@
     </row>
     <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>112</v>
@@ -9541,7 +9596,7 @@
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>112</v>
@@ -9555,13 +9610,13 @@
     </row>
     <row r="26" spans="7:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="G26" s="31" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>178</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>112</v>
@@ -9569,13 +9624,13 @@
     </row>
     <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K27" s="31" t="s">
         <v>301</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="K27" s="31" t="s">
-        <v>305</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>112</v>
@@ -9583,24 +9638,24 @@
     </row>
     <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G28" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K28" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="K28" s="43" t="s">
-        <v>306</v>
-      </c>
       <c r="L28" s="36" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="H29" s="36" t="s">
         <v>255</v>
-      </c>
-      <c r="H29" s="36" t="s">
-        <v>257</v>
       </c>
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
